--- a/data/nzd0144/nzd0144.xlsx
+++ b/data/nzd0144/nzd0144.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K658"/>
+  <dimension ref="A1:K663"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26094,6 +26094,201 @@
         <v>354.69</v>
       </c>
       <c r="K658" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:11:19+00:00</t>
+        </is>
+      </c>
+      <c r="B659" t="n">
+        <v>365.49</v>
+      </c>
+      <c r="C659" t="n">
+        <v>360.85</v>
+      </c>
+      <c r="D659" t="n">
+        <v>363.81</v>
+      </c>
+      <c r="E659" t="n">
+        <v>363.01</v>
+      </c>
+      <c r="F659" t="n">
+        <v>364.94</v>
+      </c>
+      <c r="G659" t="n">
+        <v>366.57</v>
+      </c>
+      <c r="H659" t="n">
+        <v>368.69</v>
+      </c>
+      <c r="I659" t="n">
+        <v>363.96</v>
+      </c>
+      <c r="J659" t="n">
+        <v>354.96</v>
+      </c>
+      <c r="K659" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B660" t="n">
+        <v>366.33</v>
+      </c>
+      <c r="C660" t="n">
+        <v>361.7</v>
+      </c>
+      <c r="D660" t="n">
+        <v>364.22</v>
+      </c>
+      <c r="E660" t="n">
+        <v>363.2</v>
+      </c>
+      <c r="F660" t="n">
+        <v>364.89</v>
+      </c>
+      <c r="G660" t="n">
+        <v>366.6</v>
+      </c>
+      <c r="H660" t="n">
+        <v>368.97</v>
+      </c>
+      <c r="I660" t="n">
+        <v>364.15</v>
+      </c>
+      <c r="J660" t="n">
+        <v>356.05</v>
+      </c>
+      <c r="K660" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B661" t="n">
+        <v>366.74</v>
+      </c>
+      <c r="C661" t="n">
+        <v>362.29</v>
+      </c>
+      <c r="D661" t="n">
+        <v>364.42</v>
+      </c>
+      <c r="E661" t="n">
+        <v>362.96</v>
+      </c>
+      <c r="F661" t="n">
+        <v>364.54</v>
+      </c>
+      <c r="G661" t="n">
+        <v>366.24</v>
+      </c>
+      <c r="H661" t="n">
+        <v>368.43</v>
+      </c>
+      <c r="I661" t="n">
+        <v>363.34</v>
+      </c>
+      <c r="J661" t="n">
+        <v>354.63</v>
+      </c>
+      <c r="K661" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:05:08+00:00</t>
+        </is>
+      </c>
+      <c r="B662" t="n">
+        <v>366.74</v>
+      </c>
+      <c r="C662" t="n">
+        <v>362.06</v>
+      </c>
+      <c r="D662" t="n">
+        <v>364.46</v>
+      </c>
+      <c r="E662" t="n">
+        <v>362.96</v>
+      </c>
+      <c r="F662" t="n">
+        <v>364.54</v>
+      </c>
+      <c r="G662" t="n">
+        <v>366.24</v>
+      </c>
+      <c r="H662" t="n">
+        <v>368.43</v>
+      </c>
+      <c r="I662" t="n">
+        <v>363.34</v>
+      </c>
+      <c r="J662" t="n">
+        <v>354.63</v>
+      </c>
+      <c r="K662" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:24+00:00</t>
+        </is>
+      </c>
+      <c r="B663" t="n">
+        <v>366.93</v>
+      </c>
+      <c r="C663" t="n">
+        <v>362.04</v>
+      </c>
+      <c r="D663" t="n">
+        <v>364.74</v>
+      </c>
+      <c r="E663" t="n">
+        <v>363</v>
+      </c>
+      <c r="F663" t="n">
+        <v>364.53</v>
+      </c>
+      <c r="G663" t="n">
+        <v>366.32</v>
+      </c>
+      <c r="H663" t="n">
+        <v>368.22</v>
+      </c>
+      <c r="I663" t="n">
+        <v>363.25</v>
+      </c>
+      <c r="J663" t="n">
+        <v>354.01</v>
+      </c>
+      <c r="K663" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -26110,7 +26305,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B676"/>
+  <dimension ref="A1:B681"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32873,6 +33068,56 @@
       </c>
       <c r="B676" t="n">
         <v>-0.86</v>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B677" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B678" t="n">
+        <v>-1.2</v>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B679" t="n">
+        <v>-1.03</v>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B680" t="n">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B681" t="n">
+        <v>-0.29</v>
       </c>
     </row>
   </sheetData>
@@ -33041,28 +33286,28 @@
         <v>0.06560000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2754682561973847</v>
+        <v>-0.2718007710117238</v>
       </c>
       <c r="J2" t="n">
-        <v>657</v>
+        <v>662</v>
       </c>
       <c r="K2" t="n">
-        <v>654</v>
+        <v>659</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3057105901769908</v>
+        <v>0.3025060825714149</v>
       </c>
       <c r="M2" t="n">
-        <v>2.528899887711211</v>
+        <v>2.529098177812668</v>
       </c>
       <c r="N2" t="n">
-        <v>9.548596136424182</v>
+        <v>9.523086107233555</v>
       </c>
       <c r="O2" t="n">
-        <v>3.090080279931928</v>
+        <v>3.085949790134887</v>
       </c>
       <c r="P2" t="n">
-        <v>371.3900557327528</v>
+        <v>371.3503782178443</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -33119,28 +33364,28 @@
         <v>0.1137</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2138998093716463</v>
+        <v>-0.2124679330537717</v>
       </c>
       <c r="J3" t="n">
-        <v>657</v>
+        <v>662</v>
       </c>
       <c r="K3" t="n">
-        <v>654</v>
+        <v>659</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2630188853247398</v>
+        <v>0.2633922169315662</v>
       </c>
       <c r="M3" t="n">
-        <v>2.218142553942371</v>
+        <v>2.209221084335228</v>
       </c>
       <c r="N3" t="n">
-        <v>7.103241318259931</v>
+        <v>7.058138579049778</v>
       </c>
       <c r="O3" t="n">
-        <v>2.665190672027038</v>
+        <v>2.656715750517879</v>
       </c>
       <c r="P3" t="n">
-        <v>366.5807118089966</v>
+        <v>366.5652178860015</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -33197,28 +33442,28 @@
         <v>0.09810000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1837895309101661</v>
+        <v>-0.1820303311158958</v>
       </c>
       <c r="J4" t="n">
-        <v>657</v>
+        <v>662</v>
       </c>
       <c r="K4" t="n">
-        <v>657</v>
+        <v>662</v>
       </c>
       <c r="L4" t="n">
-        <v>0.262252142274482</v>
+        <v>0.2613413236867093</v>
       </c>
       <c r="M4" t="n">
-        <v>1.841681895564129</v>
+        <v>1.83596797146792</v>
       </c>
       <c r="N4" t="n">
-        <v>5.245476304944851</v>
+        <v>5.216865527689881</v>
       </c>
       <c r="O4" t="n">
-        <v>2.290300483549015</v>
+        <v>2.284045868123029</v>
       </c>
       <c r="P4" t="n">
-        <v>368.090995911722</v>
+        <v>368.0719439791702</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -33275,28 +33520,28 @@
         <v>0.0948</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2242240924082327</v>
+        <v>-0.2229147497334638</v>
       </c>
       <c r="J5" t="n">
-        <v>657</v>
+        <v>662</v>
       </c>
       <c r="K5" t="n">
-        <v>657</v>
+        <v>662</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3934682686259918</v>
+        <v>0.3943200746178199</v>
       </c>
       <c r="M5" t="n">
-        <v>1.661702924522044</v>
+        <v>1.656547680097695</v>
       </c>
       <c r="N5" t="n">
-        <v>4.278217305307146</v>
+        <v>4.251657881198417</v>
       </c>
       <c r="O5" t="n">
-        <v>2.06838519268224</v>
+        <v>2.061954868855867</v>
       </c>
       <c r="P5" t="n">
-        <v>368.1757795383592</v>
+        <v>368.1616032800242</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -33353,28 +33598,28 @@
         <v>0.08210000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2553309739495465</v>
+        <v>-0.2547381714705441</v>
       </c>
       <c r="J6" t="n">
-        <v>657</v>
+        <v>662</v>
       </c>
       <c r="K6" t="n">
-        <v>657</v>
+        <v>662</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3930205662028039</v>
+        <v>0.3958222383188702</v>
       </c>
       <c r="M6" t="n">
-        <v>1.942865769269008</v>
+        <v>1.930694012290093</v>
       </c>
       <c r="N6" t="n">
-        <v>5.558020973580408</v>
+        <v>5.517457631458727</v>
       </c>
       <c r="O6" t="n">
-        <v>2.357545540086216</v>
+        <v>2.34892691062509</v>
       </c>
       <c r="P6" t="n">
-        <v>371.1536511102108</v>
+        <v>371.147234930859</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -33431,28 +33676,28 @@
         <v>0.0945</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1250050299112791</v>
+        <v>-0.1276839087926657</v>
       </c>
       <c r="J7" t="n">
-        <v>657</v>
+        <v>662</v>
       </c>
       <c r="K7" t="n">
-        <v>657</v>
+        <v>662</v>
       </c>
       <c r="L7" t="n">
-        <v>0.08659250545419261</v>
+        <v>0.09115766103386502</v>
       </c>
       <c r="M7" t="n">
-        <v>2.389774603604774</v>
+        <v>2.384174125392364</v>
       </c>
       <c r="N7" t="n">
-        <v>9.099001155397961</v>
+        <v>9.054284219132509</v>
       </c>
       <c r="O7" t="n">
-        <v>3.016455064375725</v>
+        <v>3.009033768360287</v>
       </c>
       <c r="P7" t="n">
-        <v>371.5530270830652</v>
+        <v>371.5820333686916</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -33509,28 +33754,28 @@
         <v>0.078</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1348207101260597</v>
+        <v>-0.1368193559633743</v>
       </c>
       <c r="J8" t="n">
-        <v>657</v>
+        <v>662</v>
       </c>
       <c r="K8" t="n">
-        <v>657</v>
+        <v>662</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1375308188398784</v>
+        <v>0.142817162200517</v>
       </c>
       <c r="M8" t="n">
-        <v>1.841041102781384</v>
+        <v>1.836594333075662</v>
       </c>
       <c r="N8" t="n">
-        <v>6.292326588548414</v>
+        <v>6.258561995364429</v>
       </c>
       <c r="O8" t="n">
-        <v>2.50845103371551</v>
+        <v>2.501711813012128</v>
       </c>
       <c r="P8" t="n">
-        <v>373.51394589764</v>
+        <v>373.5355885613656</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -33587,28 +33832,28 @@
         <v>0.08599999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1397373604045797</v>
+        <v>-0.1410236212351549</v>
       </c>
       <c r="J9" t="n">
-        <v>657</v>
+        <v>662</v>
       </c>
       <c r="K9" t="n">
-        <v>657</v>
+        <v>662</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1133422887464616</v>
+        <v>0.1168231488152125</v>
       </c>
       <c r="M9" t="n">
-        <v>2.350890409474283</v>
+        <v>2.339270366006915</v>
       </c>
       <c r="N9" t="n">
-        <v>8.43225179094906</v>
+        <v>8.375078788615735</v>
       </c>
       <c r="O9" t="n">
-        <v>2.903833981299389</v>
+        <v>2.893972838265027</v>
       </c>
       <c r="P9" t="n">
-        <v>368.2286659771195</v>
+        <v>368.2425968618372</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -33665,28 +33910,28 @@
         <v>0.1037</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2204365069158547</v>
+        <v>-0.227008140710854</v>
       </c>
       <c r="J10" t="n">
-        <v>657</v>
+        <v>662</v>
       </c>
       <c r="K10" t="n">
-        <v>657</v>
+        <v>662</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1755299376506281</v>
+        <v>0.1849431108495746</v>
       </c>
       <c r="M10" t="n">
-        <v>2.822063258332189</v>
+        <v>2.835273009598258</v>
       </c>
       <c r="N10" t="n">
-        <v>12.59926502052286</v>
+        <v>12.65083043198796</v>
       </c>
       <c r="O10" t="n">
-        <v>3.549544339844603</v>
+        <v>3.556800589292006</v>
       </c>
       <c r="P10" t="n">
-        <v>365.1920694588003</v>
+        <v>365.2632283050534</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -33724,7 +33969,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K658"/>
+  <dimension ref="A1:K663"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -71209,6 +71454,291 @@
         </is>
       </c>
     </row>
+    <row r="659">
+      <c r="A659" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:11:19+00:00</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>-36.62208169580348,174.76589751328478</t>
+        </is>
+      </c>
+      <c r="C659" t="inlineStr">
+        <is>
+          <t>-36.62180304717285,174.76672821581354</t>
+        </is>
+      </c>
+      <c r="D659" t="inlineStr">
+        <is>
+          <t>-36.62145660786623,174.76751037993884</t>
+        </is>
+      </c>
+      <c r="E659" t="inlineStr">
+        <is>
+          <t>-36.62102185817925,174.7682223365397</t>
+        </is>
+      </c>
+      <c r="F659" t="inlineStr">
+        <is>
+          <t>-36.620566857736726,174.7689161327671</t>
+        </is>
+      </c>
+      <c r="G659" t="inlineStr">
+        <is>
+          <t>-36.620068517257614,174.76955277840048</t>
+        </is>
+      </c>
+      <c r="H659" t="inlineStr">
+        <is>
+          <t>-36.619525640639345,174.77012356673475</t>
+        </is>
+      </c>
+      <c r="I659" t="inlineStr">
+        <is>
+          <t>-36.618929900416326,174.77061695206876</t>
+        </is>
+      </c>
+      <c r="J659" t="inlineStr">
+        <is>
+          <t>-36.618346223229175,174.7711556873893</t>
+        </is>
+      </c>
+      <c r="K659" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>-36.62207493418244,174.76589328990678</t>
+        </is>
+      </c>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>-36.621796231231684,174.76672387828273</t>
+        </is>
+      </c>
+      <c r="D660" t="inlineStr">
+        <is>
+          <t>-36.62145351327101,174.76750787514283</t>
+        </is>
+      </c>
+      <c r="E660" t="inlineStr">
+        <is>
+          <t>-36.62102052082672,174.7682210099218</t>
+        </is>
+      </c>
+      <c r="F660" t="inlineStr">
+        <is>
+          <t>-36.62056719635504,174.7689165015874</t>
+        </is>
+      </c>
+      <c r="G660" t="inlineStr">
+        <is>
+          <t>-36.62006833138741,174.76955253482726</t>
+        </is>
+      </c>
+      <c r="H660" t="inlineStr">
+        <is>
+          <t>-36.619524189557275,174.77012100567524</t>
+        </is>
+      </c>
+      <c r="I660" t="inlineStr">
+        <is>
+          <t>-36.6189290594218,174.77061510172862</t>
+        </is>
+      </c>
+      <c r="J660" t="inlineStr">
+        <is>
+          <t>-36.61834139860895,174.77114507234012</t>
+        </is>
+      </c>
+      <c r="K660" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>-36.62207163386736,174.76589122849637</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>-36.621791500166516,174.7667208675265</t>
+        </is>
+      </c>
+      <c r="D661" t="inlineStr">
+        <is>
+          <t>-36.62145200371235,174.7675066532912</t>
+        </is>
+      </c>
+      <c r="E661" t="inlineStr">
+        <is>
+          <t>-36.62102221011413,174.7682226856497</t>
+        </is>
+      </c>
+      <c r="F661" t="inlineStr">
+        <is>
+          <t>-36.620569566683265,174.76891908332976</t>
+        </is>
+      </c>
+      <c r="G661" t="inlineStr">
+        <is>
+          <t>-36.620070561829934,174.76955545770616</t>
+        </is>
+      </c>
+      <c r="H661" t="inlineStr">
+        <is>
+          <t>-36.619526988072664,174.77012594486155</t>
+        </is>
+      </c>
+      <c r="I661" t="inlineStr">
+        <is>
+          <t>-36.618932644714015,174.770622990021</t>
+        </is>
+      </c>
+      <c r="J661" t="inlineStr">
+        <is>
+          <t>-36.61834768389382,174.77115890112003</t>
+        </is>
+      </c>
+      <c r="K661" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:05:08+00:00</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>-36.62207163386736,174.76589122849637</t>
+        </is>
+      </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>-36.62179334448007,174.7667220412111</t>
+        </is>
+      </c>
+      <c r="D662" t="inlineStr">
+        <is>
+          <t>-36.6214517018006,174.76750640892087</t>
+        </is>
+      </c>
+      <c r="E662" t="inlineStr">
+        <is>
+          <t>-36.62102221011413,174.7682226856497</t>
+        </is>
+      </c>
+      <c r="F662" t="inlineStr">
+        <is>
+          <t>-36.620569566683265,174.76891908332976</t>
+        </is>
+      </c>
+      <c r="G662" t="inlineStr">
+        <is>
+          <t>-36.620070561829934,174.76955545770616</t>
+        </is>
+      </c>
+      <c r="H662" t="inlineStr">
+        <is>
+          <t>-36.619526988072664,174.77012594486155</t>
+        </is>
+      </c>
+      <c r="I662" t="inlineStr">
+        <is>
+          <t>-36.618932644714015,174.770622990021</t>
+        </is>
+      </c>
+      <c r="J662" t="inlineStr">
+        <is>
+          <t>-36.61834768389382,174.77115890112003</t>
+        </is>
+      </c>
+      <c r="K662" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:24+00:00</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>-36.62207010445304,174.76589027320867</t>
+        </is>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>-36.62179350485516,174.7667221432706</t>
+        </is>
+      </c>
+      <c r="D663" t="inlineStr">
+        <is>
+          <t>-36.62144958841845,174.76750469832865</t>
+        </is>
+      </c>
+      <c r="E663" t="inlineStr">
+        <is>
+          <t>-36.62102192856622,174.76822240636173</t>
+        </is>
+      </c>
+      <c r="F663" t="inlineStr">
+        <is>
+          <t>-36.620569634406934,174.76891915709382</t>
+        </is>
+      </c>
+      <c r="G663" t="inlineStr">
+        <is>
+          <t>-36.620070066176055,174.76955480817747</t>
+        </is>
+      </c>
+      <c r="H663" t="inlineStr">
+        <is>
+          <t>-36.61952807638415,174.77012786565635</t>
+        </is>
+      </c>
+      <c r="I663" t="inlineStr">
+        <is>
+          <t>-36.618933043079785,174.77062386649794</t>
+        </is>
+      </c>
+      <c r="J663" t="inlineStr">
+        <is>
+          <t>-36.61835042817262,174.77116493903873</t>
+        </is>
+      </c>
+      <c r="K663" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0144/nzd0144.xlsx
+++ b/data/nzd0144/nzd0144.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K663"/>
+  <dimension ref="A1:K668"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26289,6 +26289,201 @@
         <v>354.01</v>
       </c>
       <c r="K663" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B664" t="n">
+        <v>368.53</v>
+      </c>
+      <c r="C664" t="n">
+        <v>362.74</v>
+      </c>
+      <c r="D664" t="n">
+        <v>365.64</v>
+      </c>
+      <c r="E664" t="n">
+        <v>363.87</v>
+      </c>
+      <c r="F664" t="n">
+        <v>365.31</v>
+      </c>
+      <c r="G664" t="n">
+        <v>366.66</v>
+      </c>
+      <c r="H664" t="n">
+        <v>368.66</v>
+      </c>
+      <c r="I664" t="n">
+        <v>363.37</v>
+      </c>
+      <c r="J664" t="n">
+        <v>353.85</v>
+      </c>
+      <c r="K664" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:16+00:00</t>
+        </is>
+      </c>
+      <c r="B665" t="n">
+        <v>368.88</v>
+      </c>
+      <c r="C665" t="n">
+        <v>362.96</v>
+      </c>
+      <c r="D665" t="n">
+        <v>365.84</v>
+      </c>
+      <c r="E665" t="n">
+        <v>364.2</v>
+      </c>
+      <c r="F665" t="n">
+        <v>365.59</v>
+      </c>
+      <c r="G665" t="n">
+        <v>366.87</v>
+      </c>
+      <c r="H665" t="n">
+        <v>369.05</v>
+      </c>
+      <c r="I665" t="n">
+        <v>363.31</v>
+      </c>
+      <c r="J665" t="n">
+        <v>353.47</v>
+      </c>
+      <c r="K665" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-13 22:05:27+00:00</t>
+        </is>
+      </c>
+      <c r="B666" t="n">
+        <v>369.2</v>
+      </c>
+      <c r="C666" t="n">
+        <v>363.14</v>
+      </c>
+      <c r="D666" t="n">
+        <v>365.96</v>
+      </c>
+      <c r="E666" t="n">
+        <v>362.98</v>
+      </c>
+      <c r="F666" t="n">
+        <v>364.23</v>
+      </c>
+      <c r="G666" t="n">
+        <v>366.64</v>
+      </c>
+      <c r="H666" t="n">
+        <v>368.84</v>
+      </c>
+      <c r="I666" t="n">
+        <v>363.09</v>
+      </c>
+      <c r="J666" t="n">
+        <v>352.84</v>
+      </c>
+      <c r="K666" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B667" t="n">
+        <v>369.51</v>
+      </c>
+      <c r="C667" t="n">
+        <v>363.27</v>
+      </c>
+      <c r="D667" t="n">
+        <v>366.05</v>
+      </c>
+      <c r="E667" t="n">
+        <v>363.13</v>
+      </c>
+      <c r="F667" t="n">
+        <v>364.39</v>
+      </c>
+      <c r="G667" t="n">
+        <v>366.69</v>
+      </c>
+      <c r="H667" t="n">
+        <v>369.04</v>
+      </c>
+      <c r="I667" t="n">
+        <v>363.19</v>
+      </c>
+      <c r="J667" t="n">
+        <v>353.22</v>
+      </c>
+      <c r="K667" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:05:56+00:00</t>
+        </is>
+      </c>
+      <c r="B668" t="n">
+        <v>369.08</v>
+      </c>
+      <c r="C668" t="n">
+        <v>363.06</v>
+      </c>
+      <c r="D668" t="n">
+        <v>365.97</v>
+      </c>
+      <c r="E668" t="n">
+        <v>362.4</v>
+      </c>
+      <c r="F668" t="n">
+        <v>363.98</v>
+      </c>
+      <c r="G668" t="n">
+        <v>366.29</v>
+      </c>
+      <c r="H668" t="n">
+        <v>368.8</v>
+      </c>
+      <c r="I668" t="n">
+        <v>363.11</v>
+      </c>
+      <c r="J668" t="n">
+        <v>352.64</v>
+      </c>
+      <c r="K668" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -26305,7 +26500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B681"/>
+  <dimension ref="A1:B686"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33118,6 +33313,56 @@
       </c>
       <c r="B681" t="n">
         <v>-0.29</v>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B682" t="n">
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B683" t="n">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>2026-08-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B684" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B685" t="n">
+        <v>-0.14</v>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B686" t="n">
+        <v>0.5600000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -33286,28 +33531,28 @@
         <v>0.06560000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2718007710117238</v>
+        <v>-0.2644424535563694</v>
       </c>
       <c r="J2" t="n">
-        <v>662</v>
+        <v>667</v>
       </c>
       <c r="K2" t="n">
-        <v>659</v>
+        <v>664</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3025060825714149</v>
+        <v>0.2903955237141276</v>
       </c>
       <c r="M2" t="n">
-        <v>2.529098177812668</v>
+        <v>2.548926765851983</v>
       </c>
       <c r="N2" t="n">
-        <v>9.523086107233555</v>
+        <v>9.637608311912345</v>
       </c>
       <c r="O2" t="n">
-        <v>3.085949790134887</v>
+        <v>3.104449759927248</v>
       </c>
       <c r="P2" t="n">
-        <v>371.3503782178443</v>
+        <v>371.2704991063728</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -33364,28 +33609,28 @@
         <v>0.1137</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2124679330537717</v>
+        <v>-0.2092447814934571</v>
       </c>
       <c r="J3" t="n">
-        <v>662</v>
+        <v>667</v>
       </c>
       <c r="K3" t="n">
-        <v>659</v>
+        <v>664</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2633922169315662</v>
+        <v>0.2596569113081054</v>
       </c>
       <c r="M3" t="n">
-        <v>2.209221084335228</v>
+        <v>2.210587864775695</v>
       </c>
       <c r="N3" t="n">
-        <v>7.058138579049778</v>
+        <v>7.040814431247211</v>
       </c>
       <c r="O3" t="n">
-        <v>2.656715750517879</v>
+        <v>2.653453303008593</v>
       </c>
       <c r="P3" t="n">
-        <v>366.5652178860015</v>
+        <v>366.5302281228848</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -33442,28 +33687,28 @@
         <v>0.09810000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1820303311158958</v>
+        <v>-0.1780255904493779</v>
       </c>
       <c r="J4" t="n">
-        <v>662</v>
+        <v>667</v>
       </c>
       <c r="K4" t="n">
-        <v>662</v>
+        <v>667</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2613413236867093</v>
+        <v>0.2539485449816026</v>
       </c>
       <c r="M4" t="n">
-        <v>1.83596797146792</v>
+        <v>1.84085281183893</v>
       </c>
       <c r="N4" t="n">
-        <v>5.216865527689881</v>
+        <v>5.232541951919736</v>
       </c>
       <c r="O4" t="n">
-        <v>2.284045868123029</v>
+        <v>2.287475016676627</v>
       </c>
       <c r="P4" t="n">
-        <v>368.0719439791702</v>
+        <v>368.028429308441</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -33520,28 +33765,28 @@
         <v>0.0948</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2229147497334638</v>
+        <v>-0.2212065874183644</v>
       </c>
       <c r="J5" t="n">
-        <v>662</v>
+        <v>667</v>
       </c>
       <c r="K5" t="n">
-        <v>662</v>
+        <v>667</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3943200746178199</v>
+        <v>0.3938182676883619</v>
       </c>
       <c r="M5" t="n">
-        <v>1.656547680097695</v>
+        <v>1.653737720711504</v>
       </c>
       <c r="N5" t="n">
-        <v>4.251657881198417</v>
+        <v>4.232801429474212</v>
       </c>
       <c r="O5" t="n">
-        <v>2.061954868855867</v>
+        <v>2.057377318207385</v>
       </c>
       <c r="P5" t="n">
-        <v>368.1616032800242</v>
+        <v>368.1430539110655</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -33598,28 +33843,28 @@
         <v>0.08210000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2547381714705441</v>
+        <v>-0.2541188580713725</v>
       </c>
       <c r="J6" t="n">
-        <v>662</v>
+        <v>667</v>
       </c>
       <c r="K6" t="n">
-        <v>662</v>
+        <v>667</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3958222383188702</v>
+        <v>0.3983876058089343</v>
       </c>
       <c r="M6" t="n">
-        <v>1.930694012290093</v>
+        <v>1.919881440458459</v>
       </c>
       <c r="N6" t="n">
-        <v>5.517457631458727</v>
+        <v>5.48036574071387</v>
       </c>
       <c r="O6" t="n">
-        <v>2.34892691062509</v>
+        <v>2.341018099185453</v>
       </c>
       <c r="P6" t="n">
-        <v>371.147234930859</v>
+        <v>371.140515633644</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -33676,28 +33921,28 @@
         <v>0.0945</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1276839087926657</v>
+        <v>-0.1298993349378292</v>
       </c>
       <c r="J7" t="n">
-        <v>662</v>
+        <v>667</v>
       </c>
       <c r="K7" t="n">
-        <v>662</v>
+        <v>667</v>
       </c>
       <c r="L7" t="n">
-        <v>0.09115766103386502</v>
+        <v>0.09528903031425662</v>
       </c>
       <c r="M7" t="n">
-        <v>2.384174125392364</v>
+        <v>2.376571758006862</v>
       </c>
       <c r="N7" t="n">
-        <v>9.054284219132509</v>
+        <v>9.003380409468793</v>
       </c>
       <c r="O7" t="n">
-        <v>3.009033768360287</v>
+        <v>3.000563348684509</v>
       </c>
       <c r="P7" t="n">
-        <v>371.5820333686916</v>
+        <v>371.6061072740345</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -33754,28 +33999,28 @@
         <v>0.078</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1368193559633743</v>
+        <v>-0.138237809019319</v>
       </c>
       <c r="J8" t="n">
-        <v>662</v>
+        <v>667</v>
       </c>
       <c r="K8" t="n">
-        <v>662</v>
+        <v>667</v>
       </c>
       <c r="L8" t="n">
-        <v>0.142817162200517</v>
+        <v>0.1472637197442461</v>
       </c>
       <c r="M8" t="n">
-        <v>1.836594333075662</v>
+        <v>1.829487352033139</v>
       </c>
       <c r="N8" t="n">
-        <v>6.258561995364429</v>
+        <v>6.21866919320667</v>
       </c>
       <c r="O8" t="n">
-        <v>2.501711813012128</v>
+        <v>2.493725965940659</v>
       </c>
       <c r="P8" t="n">
-        <v>373.5355885613656</v>
+        <v>373.5510002248536</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -33832,28 +34077,28 @@
         <v>0.08599999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1410236212351549</v>
+        <v>-0.1428222517470061</v>
       </c>
       <c r="J9" t="n">
-        <v>662</v>
+        <v>667</v>
       </c>
       <c r="K9" t="n">
-        <v>662</v>
+        <v>667</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1168231488152125</v>
+        <v>0.1210537565006082</v>
       </c>
       <c r="M9" t="n">
-        <v>2.339270366006915</v>
+        <v>2.330236531167073</v>
       </c>
       <c r="N9" t="n">
-        <v>8.375078788615735</v>
+        <v>8.323396657446329</v>
       </c>
       <c r="O9" t="n">
-        <v>2.893972838265027</v>
+        <v>2.885029749837309</v>
       </c>
       <c r="P9" t="n">
-        <v>368.2425968618372</v>
+        <v>368.26214093837</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -33910,28 +34155,28 @@
         <v>0.1037</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.227008140710854</v>
+        <v>-0.2357086299487007</v>
       </c>
       <c r="J10" t="n">
-        <v>662</v>
+        <v>667</v>
       </c>
       <c r="K10" t="n">
-        <v>662</v>
+        <v>667</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1849431108495746</v>
+        <v>0.1959096987741142</v>
       </c>
       <c r="M10" t="n">
-        <v>2.835273009598258</v>
+        <v>2.859467814404503</v>
       </c>
       <c r="N10" t="n">
-        <v>12.65083043198796</v>
+        <v>12.81517822452603</v>
       </c>
       <c r="O10" t="n">
-        <v>3.556800589292006</v>
+        <v>3.579829356900413</v>
       </c>
       <c r="P10" t="n">
-        <v>365.2632283050534</v>
+        <v>365.3577679449268</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -33969,7 +34214,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K663"/>
+  <dimension ref="A1:K668"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -71739,6 +71984,291 @@
         </is>
       </c>
     </row>
+    <row r="664">
+      <c r="A664" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>-36.62205722517417,174.76588222868227</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>-36.62178789172694,174.76671857118725</t>
+        </is>
+      </c>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>-36.62144279540418,174.76749919999722</t>
+        </is>
+      </c>
+      <c r="E664" t="inlineStr">
+        <is>
+          <t>-36.62101580489924,174.7682163318485</t>
+        </is>
+      </c>
+      <c r="F664" t="inlineStr">
+        <is>
+          <t>-36.620564351961086,174.76891340349678</t>
+        </is>
+      </c>
+      <c r="G664" t="inlineStr">
+        <is>
+          <t>-36.62006795964697,174.76955204768078</t>
+        </is>
+      </c>
+      <c r="H664" t="inlineStr">
+        <is>
+          <t>-36.61952579611243,174.77012384113402</t>
+        </is>
+      </c>
+      <c r="I664" t="inlineStr">
+        <is>
+          <t>-36.618932511925415,174.77062269786197</t>
+        </is>
+      </c>
+      <c r="J664" t="inlineStr">
+        <is>
+          <t>-36.61835113637354,174.77116649721137</t>
+        </is>
+      </c>
+      <c r="K664" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:16+00:00</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>-36.62205440783184,174.7658804689425</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>-36.62178612760088,174.7667174485326</t>
+        </is>
+      </c>
+      <c r="D665" t="inlineStr">
+        <is>
+          <t>-36.62144128584541,174.7674979781459</t>
+        </is>
+      </c>
+      <c r="E665" t="inlineStr">
+        <is>
+          <t>-36.6210134821289,174.76821402772308</t>
+        </is>
+      </c>
+      <c r="F665" t="inlineStr">
+        <is>
+          <t>-36.62056245569839,174.76891133810318</t>
+        </is>
+      </c>
+      <c r="G665" t="inlineStr">
+        <is>
+          <t>-36.620066658555444,174.76955034266817</t>
+        </is>
+      </c>
+      <c r="H665" t="inlineStr">
+        <is>
+          <t>-36.619523774962374,174.77012027394397</t>
+        </is>
+      </c>
+      <c r="I665" t="inlineStr">
+        <is>
+          <t>-36.6189327775026,174.77062328217997</t>
+        </is>
+      </c>
+      <c r="J665" t="inlineStr">
+        <is>
+          <t>-36.61835281835065,174.77117019787147</t>
+        </is>
+      </c>
+      <c r="K665" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-13 22:05:27+00:00</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>-36.62205183197595,174.76587886003767</t>
+        </is>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>-36.621784684225034,174.766716529997</t>
+        </is>
+      </c>
+      <c r="D666" t="inlineStr">
+        <is>
+          <t>-36.62144038011014,174.76749724503517</t>
+        </is>
+      </c>
+      <c r="E666" t="inlineStr">
+        <is>
+          <t>-36.621022069340185,174.76822254600572</t>
+        </is>
+      </c>
+      <c r="F666" t="inlineStr">
+        <is>
+          <t>-36.620571666116795,174.768921370016</t>
+        </is>
+      </c>
+      <c r="G666" t="inlineStr">
+        <is>
+          <t>-36.62006808356044,174.76955221006295</t>
+        </is>
+      </c>
+      <c r="H666" t="inlineStr">
+        <is>
+          <t>-36.61952486327396,174.77012219473858</t>
+        </is>
+      </c>
+      <c r="I666" t="inlineStr">
+        <is>
+          <t>-36.618933751285574,174.77062542467925</t>
+        </is>
+      </c>
+      <c r="J666" t="inlineStr">
+        <is>
+          <t>-36.618355606891384,174.77117633317678</t>
+        </is>
+      </c>
+      <c r="K666" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>-36.622049336615554,174.76587730141122</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>-36.62178364178691,174.7667158666102</t>
+        </is>
+      </c>
+      <c r="D667" t="inlineStr">
+        <is>
+          <t>-36.621439700808686,174.76749669520208</t>
+        </is>
+      </c>
+      <c r="E667" t="inlineStr">
+        <is>
+          <t>-36.621021013535554,174.76822149867576</t>
+        </is>
+      </c>
+      <c r="F667" t="inlineStr">
+        <is>
+          <t>-36.62057058253821,174.76892018979083</t>
+        </is>
+      </c>
+      <c r="G667" t="inlineStr">
+        <is>
+          <t>-36.62006777377675,174.76955180410755</t>
+        </is>
+      </c>
+      <c r="H667" t="inlineStr">
+        <is>
+          <t>-36.61952382678674,174.77012036541038</t>
+        </is>
+      </c>
+      <c r="I667" t="inlineStr">
+        <is>
+          <t>-36.61893330865695,174.77062445081594</t>
+        </is>
+      </c>
+      <c r="J667" t="inlineStr">
+        <is>
+          <t>-36.618353924914466,174.7711726325164</t>
+        </is>
+      </c>
+      <c r="K667" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:05:56+00:00</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>-36.62205279792191,174.76587946337696</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>-36.62178532572541,174.76671693823505</t>
+        </is>
+      </c>
+      <c r="D668" t="inlineStr">
+        <is>
+          <t>-36.6214403046322,174.7674971839426</t>
+        </is>
+      </c>
+      <c r="E668" t="inlineStr">
+        <is>
+          <t>-36.62102615178464,174.76822659568174</t>
+        </is>
+      </c>
+      <c r="F668" t="inlineStr">
+        <is>
+          <t>-36.62057335920831,174.76892321411785</t>
+        </is>
+      </c>
+      <c r="G668" t="inlineStr">
+        <is>
+          <t>-36.62007025204626,174.76955505175076</t>
+        </is>
+      </c>
+      <c r="H668" t="inlineStr">
+        <is>
+          <t>-36.61952507057139,174.77012256060422</t>
+        </is>
+      </c>
+      <c r="I668" t="inlineStr">
+        <is>
+          <t>-36.61893366275985,174.77062522990659</t>
+        </is>
+      </c>
+      <c r="J668" t="inlineStr">
+        <is>
+          <t>-36.61835649214234,174.77117828089283</t>
+        </is>
+      </c>
+      <c r="K668" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0144/nzd0144.xlsx
+++ b/data/nzd0144/nzd0144.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K668"/>
+  <dimension ref="A1:K669"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26484,6 +26484,45 @@
         <v>352.64</v>
       </c>
       <c r="K668" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:05:36+00:00</t>
+        </is>
+      </c>
+      <c r="B669" t="n">
+        <v>369.1</v>
+      </c>
+      <c r="C669" t="n">
+        <v>363.4</v>
+      </c>
+      <c r="D669" t="n">
+        <v>366.24</v>
+      </c>
+      <c r="E669" t="n">
+        <v>362.19</v>
+      </c>
+      <c r="F669" t="n">
+        <v>363.97</v>
+      </c>
+      <c r="G669" t="n">
+        <v>366.09</v>
+      </c>
+      <c r="H669" t="n">
+        <v>368.99</v>
+      </c>
+      <c r="I669" t="n">
+        <v>363.48</v>
+      </c>
+      <c r="J669" t="n">
+        <v>353.19</v>
+      </c>
+      <c r="K669" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -26500,7 +26539,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B686"/>
+  <dimension ref="A1:B687"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33363,6 +33402,16 @@
       </c>
       <c r="B686" t="n">
         <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B687" t="n">
+        <v>1.13</v>
       </c>
     </row>
   </sheetData>
@@ -33531,28 +33580,28 @@
         <v>0.06560000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2644424535563694</v>
+        <v>-0.2629787009056326</v>
       </c>
       <c r="J2" t="n">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="K2" t="n">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2903955237141276</v>
+        <v>0.2879910381866843</v>
       </c>
       <c r="M2" t="n">
-        <v>2.548926765851983</v>
+        <v>2.552838040375491</v>
       </c>
       <c r="N2" t="n">
-        <v>9.637608311912345</v>
+        <v>9.660245592923896</v>
       </c>
       <c r="O2" t="n">
-        <v>3.104449759927248</v>
+        <v>3.108093562446906</v>
       </c>
       <c r="P2" t="n">
-        <v>371.2704991063728</v>
+        <v>371.2545525428953</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -33609,28 +33658,28 @@
         <v>0.1137</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2092447814934571</v>
+        <v>-0.2085014398341574</v>
       </c>
       <c r="J3" t="n">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="K3" t="n">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2596569113081054</v>
+        <v>0.2586539696367434</v>
       </c>
       <c r="M3" t="n">
-        <v>2.210587864775695</v>
+        <v>2.2114227947362</v>
       </c>
       <c r="N3" t="n">
-        <v>7.040814431247211</v>
+        <v>7.039802332290084</v>
       </c>
       <c r="O3" t="n">
-        <v>2.653453303008593</v>
+        <v>2.653262582612223</v>
       </c>
       <c r="P3" t="n">
-        <v>366.5302281228848</v>
+        <v>366.5221299343353</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -33687,28 +33736,28 @@
         <v>0.09810000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1780255904493779</v>
+        <v>-0.1771358548848304</v>
       </c>
       <c r="J4" t="n">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="K4" t="n">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2539485449816026</v>
+        <v>0.2521778284289191</v>
       </c>
       <c r="M4" t="n">
-        <v>1.84085281183893</v>
+        <v>1.842242723304869</v>
       </c>
       <c r="N4" t="n">
-        <v>5.232541951919736</v>
+        <v>5.238353267812209</v>
       </c>
       <c r="O4" t="n">
-        <v>2.287475016676627</v>
+        <v>2.288744911040155</v>
       </c>
       <c r="P4" t="n">
-        <v>368.028429308441</v>
+        <v>368.0187274125524</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -33765,28 +33814,28 @@
         <v>0.0948</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2212065874183644</v>
+        <v>-0.2211975531611587</v>
       </c>
       <c r="J5" t="n">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="K5" t="n">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3938182676883619</v>
+        <v>0.3945774218051934</v>
       </c>
       <c r="M5" t="n">
-        <v>1.653737720711504</v>
+        <v>1.651312530861344</v>
       </c>
       <c r="N5" t="n">
-        <v>4.232801429474212</v>
+        <v>4.226466307146303</v>
       </c>
       <c r="O5" t="n">
-        <v>2.057377318207385</v>
+        <v>2.055837130500931</v>
       </c>
       <c r="P5" t="n">
-        <v>368.1430539110655</v>
+        <v>368.1429553992982</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -33843,28 +33892,28 @@
         <v>0.08210000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2541188580713725</v>
+        <v>-0.2542069285129769</v>
       </c>
       <c r="J6" t="n">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="K6" t="n">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3983876058089343</v>
+        <v>0.3993297999126953</v>
       </c>
       <c r="M6" t="n">
-        <v>1.919881440458459</v>
+        <v>1.917525776505971</v>
       </c>
       <c r="N6" t="n">
-        <v>5.48036574071387</v>
+        <v>5.472295289138752</v>
       </c>
       <c r="O6" t="n">
-        <v>2.341018099185453</v>
+        <v>2.339293758624331</v>
       </c>
       <c r="P6" t="n">
-        <v>371.140515633644</v>
+        <v>371.1414759754459</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -33921,28 +33970,28 @@
         <v>0.0945</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1298993349378292</v>
+        <v>-0.1304886354350556</v>
       </c>
       <c r="J7" t="n">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="K7" t="n">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="L7" t="n">
-        <v>0.09528903031425662</v>
+        <v>0.09629794224212163</v>
       </c>
       <c r="M7" t="n">
-        <v>2.376571758006862</v>
+        <v>2.3757465102313</v>
       </c>
       <c r="N7" t="n">
-        <v>9.003380409468793</v>
+        <v>8.995887901368583</v>
       </c>
       <c r="O7" t="n">
-        <v>3.000563348684509</v>
+        <v>2.999314571926156</v>
       </c>
       <c r="P7" t="n">
-        <v>371.6061072740345</v>
+        <v>371.6125331519009</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -33999,28 +34048,28 @@
         <v>0.078</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.138237809019319</v>
+        <v>-0.1384802570548783</v>
       </c>
       <c r="J8" t="n">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="K8" t="n">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1472637197442461</v>
+        <v>0.1480947684680732</v>
       </c>
       <c r="M8" t="n">
-        <v>1.829487352033139</v>
+        <v>1.827875467480639</v>
       </c>
       <c r="N8" t="n">
-        <v>6.21866919320667</v>
+        <v>6.210372953806315</v>
       </c>
       <c r="O8" t="n">
-        <v>2.493725965940659</v>
+        <v>2.49206198835549</v>
       </c>
       <c r="P8" t="n">
-        <v>373.5510002248536</v>
+        <v>373.5536439379894</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -34077,28 +34126,28 @@
         <v>0.08599999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1428222517470061</v>
+        <v>-0.1430908736390809</v>
       </c>
       <c r="J9" t="n">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="K9" t="n">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1210537565006082</v>
+        <v>0.1217865670686205</v>
       </c>
       <c r="M9" t="n">
-        <v>2.330236531167073</v>
+        <v>2.3280181252008</v>
       </c>
       <c r="N9" t="n">
-        <v>8.323396657446329</v>
+        <v>8.312180187692309</v>
       </c>
       <c r="O9" t="n">
-        <v>2.885029749837309</v>
+        <v>2.883085185646153</v>
       </c>
       <c r="P9" t="n">
-        <v>368.26214093837</v>
+        <v>368.2650700576884</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -34155,28 +34204,28 @@
         <v>0.1037</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2357086299487007</v>
+        <v>-0.2374108802250166</v>
       </c>
       <c r="J10" t="n">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="K10" t="n">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1959096987741142</v>
+        <v>0.1980859390040195</v>
       </c>
       <c r="M10" t="n">
-        <v>2.859467814404503</v>
+        <v>2.8641027804261</v>
       </c>
       <c r="N10" t="n">
-        <v>12.81517822452603</v>
+        <v>12.84593760019406</v>
       </c>
       <c r="O10" t="n">
-        <v>3.579829356900413</v>
+        <v>3.58412298898825</v>
       </c>
       <c r="P10" t="n">
-        <v>365.3577679449268</v>
+        <v>365.3763297014927</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -34214,7 +34263,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K668"/>
+  <dimension ref="A1:K669"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -72269,6 +72318,63 @@
         </is>
       </c>
     </row>
+    <row r="669">
+      <c r="A669" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:05:36+00:00</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>-36.62205263693092,174.7658793628204</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>-36.62178259934878,174.76671520322347</t>
+        </is>
+      </c>
+      <c r="D669" t="inlineStr">
+        <is>
+          <t>-36.621438266727836,174.76749553444344</t>
+        </is>
+      </c>
+      <c r="E669" t="inlineStr">
+        <is>
+          <t>-36.62102762991105,174.76822806194386</t>
+        </is>
+      </c>
+      <c r="F669" t="inlineStr">
+        <is>
+          <t>-36.620573426931976,174.76892328788193</t>
+        </is>
+      </c>
+      <c r="G669" t="inlineStr">
+        <is>
+          <t>-36.62007149118098,174.7695566755724</t>
+        </is>
+      </c>
+      <c r="H669" t="inlineStr">
+        <is>
+          <t>-36.61952408590854,174.77012082274243</t>
+        </is>
+      </c>
+      <c r="I669" t="inlineStr">
+        <is>
+          <t>-36.61893202503392,174.77062162661238</t>
+        </is>
+      </c>
+      <c r="J669" t="inlineStr">
+        <is>
+          <t>-36.61835405770213,174.77117292467378</t>
+        </is>
+      </c>
+      <c r="K669" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
